--- a/survey_templates/015_child_fitness_readiness_survey--survey_templates.xlsx
+++ b/survey_templates/015_child_fitness_readiness_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -889,8 +889,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -918,12 +918,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'daily',_'value':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Daily', 'value': 'daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'3-5_times_a_week',_'value':_'frequent'}</t>
+          <t>3-5_times_a_week</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': '3-5 times a week', 'value': 'frequent'}</t>
+          <t>3-5 times a week</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'1-2_times_a_week',_'value':_'occasional'}</t>
+          <t>1-2_times_a_week</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': '1-2 times a week', 'value': 'occasional'}</t>
+          <t>1-2 times a week</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'rarely',_'value':_'rare'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely', 'value': 'rare'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'soccer',_'value':_'soccer'}</t>
+          <t>soccer</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Soccer', 'value': 'soccer'}</t>
+          <t>Soccer</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'swimming',_'value':_'swimming'}</t>
+          <t>swimming</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Swimming', 'value': 'swimming'}</t>
+          <t>Swimming</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'basketball',_'value':_'basketball'}</t>
+          <t>basketball</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Basketball', 'value': 'basketball'}</t>
+          <t>Basketball</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'gymnastics',_'value':_'gymnastics'}</t>
+          <t>gymnastics</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Gymnastics', 'value': 'gymnastics'}</t>
+          <t>Gymnastics</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'dance',_'value':_'dance'}</t>
+          <t>dance</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Dance', 'value': 'dance'}</t>
+          <t>Dance</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'i_agree',_'value':_'agree'}</t>
+          <t>i_agree</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'I Agree', 'value': 'agree'}</t>
+          <t>I Agree</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'i_disagree',_'value':_'disagree'}</t>
+          <t>i_disagree</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'I Disagree', 'value': 'disagree'}</t>
+          <t>I Disagree</t>
         </is>
       </c>
     </row>
